--- a/output/archive/Tarnovell_Group/Integration/Pricing/2024/Price_Harmonisation_Working_v4.xlsx
+++ b/output/archive/Tarnovell_Group/Integration/Pricing/2024/Price_Harmonisation_Working_v4.xlsx
@@ -144,18 +144,18 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Sofia Lindervik</author>
     <author>Andrea Beckett</author>
-    <author>Sofia Lindervik</author>
   </authors>
   <commentList>
-    <comment ref="E7" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
-        <t>Merrivoss quotes in USD per compound incl. both species for some assays - not like for like with Brindlewythe. Normalise before comparing.</t>
+        <t>Who owns microsomal stability after integration? Needs steering group decision.</t>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="E12" authorId="1" shapeId="0">
       <text>
-        <t>Who owns microsomal stability after integration? Needs steering group decision.</t>
+        <t>Merrivoss microsomal price covers both species per compound - not like for like with Brindlewythe's single-species price. Normalise before comparing.</t>
       </text>
     </comment>
   </commentList>
@@ -449,7 +449,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -462,7 +462,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -473,6 +473,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1057,6 +1058,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -1065,7 +1067,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1162,6 +1164,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1169,10 +1172,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
@@ -1261,5 +1269,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>